--- a/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1893DBD5-B424-42BC-A6F0-F0163446BF29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A52BA14D-C88B-461F-B9A1-A0ACA94F993E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BBB1AC8-C926-4E2C-8FE6-98503F968F0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B254EC-3590-40A8-BCF5-77663D2851FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B367423-F0EE-491F-B00A-0901AC6CA2D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A48C41-1A4F-4EA3-A970-180AAB611B6F}"/>
 </file>